--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,48</t>
+          <t>2,46; 5,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,79</t>
+          <t>2,14; 4,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,12</t>
+          <t>7,16; 11,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,55</t>
+          <t>7,04; 11,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,93</t>
+          <t>8,01; 12,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 18,03</t>
+          <t>12,53; 18,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,88</t>
+          <t>5,21; 7,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,18</t>
+          <t>5,36; 8,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 14,16</t>
+          <t>10,98; 14,07</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,65</t>
+          <t>2,36; 4,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,2</t>
+          <t>2,02; 4,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,84; 7,26</t>
+          <t>2,53; 7,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 10,74</t>
+          <t>7,07; 10,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,2</t>
+          <t>6,59; 10,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 16,32</t>
+          <t>12,78; 16,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 7,1</t>
+          <t>5,08; 7,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 6,64</t>
+          <t>4,56; 6,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,96</t>
+          <t>6,3; 10,99</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,36</t>
+          <t>2,44; 5,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,26</t>
+          <t>1,87; 4,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,37</t>
+          <t>4,86; 8,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 10,31</t>
+          <t>6,43; 10,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,98</t>
+          <t>5,98; 9,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,53</t>
+          <t>4,96; 13,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,41</t>
+          <t>4,89; 7,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,6</t>
+          <t>4,17; 6,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,0</t>
+          <t>5,75; 10,26</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,01</t>
+          <t>2,53; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,84</t>
+          <t>2,49; 5,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,52</t>
+          <t>5,47; 8,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,66</t>
+          <t>8,67; 12,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,91</t>
+          <t>8,06; 12,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,62; 17,97</t>
+          <t>12,71; 18,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,59</t>
+          <t>6,2; 8,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,26</t>
+          <t>5,74; 8,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,22; 13,16</t>
+          <t>9,99; 13,0</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,25</t>
+          <t>2,92; 4,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,75</t>
+          <t>2,59; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,57</t>
+          <t>5,17; 7,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,3</t>
+          <t>8,33; 10,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 10,05</t>
+          <t>8,03; 10,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,3</t>
+          <t>11,13; 15,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,09</t>
+          <t>5,88; 7,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,66</t>
+          <t>5,52; 6,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,1; 11,33</t>
+          <t>9,07; 11,41</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17679; 38532</t>
+          <t>17316; 37528</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13357; 32299</t>
+          <t>14414; 33211</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45306; 70683</t>
+          <t>45476; 71294</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48724; 80525</t>
+          <t>49097; 82040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53925; 86992</t>
+          <t>53884; 84133</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90096; 130798</t>
+          <t>90910; 131030</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72375; 110356</t>
+          <t>73000; 109472</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73587; 110272</t>
+          <t>72279; 109597</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>146130; 192640</t>
+          <t>149450; 191451</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23149; 47361</t>
+          <t>24041; 48069</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20605; 42910</t>
+          <t>20638; 41093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33905; 86550</t>
+          <t>30216; 85957</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73167; 110838</t>
+          <t>73015; 110913</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67283; 106376</t>
+          <t>68767; 108431</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>123944; 156437</t>
+          <t>122540; 155770</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104038; 145620</t>
+          <t>104120; 149563</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>93864; 137141</t>
+          <t>94277; 140581</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136454; 235785</t>
+          <t>135459; 236472</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18496; 40612</t>
+          <t>18454; 41698</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13123; 32388</t>
+          <t>14224; 33446</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33850; 59010</t>
+          <t>34241; 61007</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49395; 80121</t>
+          <t>49971; 80562</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46233; 78370</t>
+          <t>46920; 78003</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>49738; 126249</t>
+          <t>46294; 125206</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>74890; 113693</t>
+          <t>75076; 115965</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65316; 101886</t>
+          <t>64455; 101548</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88058; 163764</t>
+          <t>94218; 168106</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23254; 47475</t>
+          <t>23970; 48495</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21930; 45346</t>
+          <t>23339; 47969</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50196; 78941</t>
+          <t>50730; 78470</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91164; 133153</t>
+          <t>91233; 132966</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84013; 124323</t>
+          <t>84092; 126192</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>138128; 196730</t>
+          <t>139164; 199102</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>122458; 171765</t>
+          <t>123951; 171462</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>113972; 163751</t>
+          <t>113650; 161732</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>206592; 266042</t>
+          <t>201938; 262928</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99877; 145479</t>
+          <t>99908; 147553</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>85975; 127247</t>
+          <t>87899; 127715</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178594; 261829</t>
+          <t>178838; 263678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>293090; 366377</t>
+          <t>296365; 365898</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>281573; 356245</t>
+          <t>284649; 358179</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>417804; 567954</t>
+          <t>413012; 567137</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>409542; 495356</t>
+          <t>410937; 492949</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>380773; 462015</t>
+          <t>382863; 464351</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>652587; 812477</t>
+          <t>650438; 818617</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,33</t>
+          <t>2,45; 5,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,92</t>
+          <t>2,15; 4,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,22</t>
+          <t>6,9; 11,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,77</t>
+          <t>6,88; 11,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,5</t>
+          <t>7,83; 12,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,53; 18,06</t>
+          <t>14,61; 18,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,82</t>
+          <t>5,17; 7,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,13</t>
+          <t>5,42; 8,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 14,07</t>
+          <t>11,49; 14,34</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,72</t>
+          <t>2,36; 4,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,02</t>
+          <t>2,02; 4,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,21</t>
+          <t>5,1; 7,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,75</t>
+          <t>7,09; 10,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,59; 10,4</t>
+          <t>6,33; 10,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 16,25</t>
+          <t>12,54; 15,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 7,3</t>
+          <t>5,13; 7,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 6,81</t>
+          <t>4,61; 6,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 10,99</t>
+          <t>9,27; 11,57</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,5</t>
+          <t>2,42; 5,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,4</t>
+          <t>1,8; 4,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,66</t>
+          <t>4,83; 8,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,37</t>
+          <t>6,52; 10,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 9,94</t>
+          <t>5,84; 10,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 13,41</t>
+          <t>10,88; 14,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,56</t>
+          <t>4,9; 7,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,57</t>
+          <t>4,29; 6,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,26</t>
+          <t>8,44; 11,09</t>
         </is>
       </c>
     </row>
@@ -965,37 +965,37 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6,88%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,74%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6,88%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,12</t>
+          <t>2,49; 5,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,12</t>
+          <t>2,49; 4,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 8,47</t>
+          <t>5,49; 8,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 12,64</t>
+          <t>8,69; 12,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,09</t>
+          <t>7,99; 11,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 18,18</t>
+          <t>14,68; 18,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,57</t>
+          <t>6,11; 8,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,16</t>
+          <t>5,75; 8,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 13,0</t>
+          <t>10,68; 13,13</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,31</t>
+          <t>2,95; 4,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,76</t>
+          <t>2,51; 3,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,62</t>
+          <t>6,2; 7,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,28</t>
+          <t>8,36; 10,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,11</t>
+          <t>7,95; 10,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,13; 15,28</t>
+          <t>14,09; 15,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,06</t>
+          <t>5,9; 7,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,69</t>
+          <t>5,52; 6,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,41</t>
+          <t>10,49; 11,77</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57440</t>
+          <t>60978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>114054</t>
+          <t>121706</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>171494</t>
+          <t>182684</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17316; 37528</t>
+          <t>17206; 39303</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14414; 33211</t>
+          <t>14513; 32065</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45476; 71294</t>
+          <t>47668; 76426</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49097; 82040</t>
+          <t>47949; 80148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53884; 84133</t>
+          <t>52693; 84575</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90910; 131030</t>
+          <t>107251; 137922</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73000; 109472</t>
+          <t>72370; 109019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>72279; 109597</t>
+          <t>73084; 110569</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>149450; 191451</t>
+          <t>163722; 204374</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>67438</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>139200</t>
+          <t>151950</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>202577</t>
+          <t>219388</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24041; 48069</t>
+          <t>24047; 46960</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20638; 41093</t>
+          <t>20632; 41926</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30216; 85957</t>
+          <t>53509; 82296</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73015; 110913</t>
+          <t>73155; 110021</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68767; 108431</t>
+          <t>65974; 105192</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122540; 155770</t>
+          <t>134342; 171005</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104120; 149563</t>
+          <t>105253; 149246</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94277; 140581</t>
+          <t>95251; 140117</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>135459; 236472</t>
+          <t>196476; 245345</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45947</t>
+          <t>50837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>104866</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>137992</t>
+          <t>155704</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18454; 41698</t>
+          <t>18371; 40691</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14224; 33446</t>
+          <t>13658; 32502</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34241; 61007</t>
+          <t>38789; 66681</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49971; 80562</t>
+          <t>50692; 81357</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>46920; 78003</t>
+          <t>45811; 79512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46294; 125206</t>
+          <t>88365; 120589</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>75076; 115965</t>
+          <t>75204; 112332</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>64455; 101548</t>
+          <t>66201; 102368</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>94218; 168106</t>
+          <t>136262; 179216</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>63767</t>
+          <t>67448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>172295</t>
+          <t>183144</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>236063</t>
+          <t>250592</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23970; 48495</t>
+          <t>23615; 49999</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23339; 47969</t>
+          <t>23347; 45117</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>50730; 78470</t>
+          <t>54331; 82027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>91233; 132966</t>
+          <t>91398; 131569</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84092; 126192</t>
+          <t>83382; 125142</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>139164; 199102</t>
+          <t>164225; 204378</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>123951; 171462</t>
+          <t>122163; 169540</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>113650; 161732</t>
+          <t>113896; 161314</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>201938; 262928</t>
+          <t>225286; 276828</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230531</t>
+          <t>246701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>517594</t>
+          <t>561666</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>748125</t>
+          <t>808367</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>99908; 147553</t>
+          <t>101165; 149257</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87899; 127715</t>
+          <t>85097; 129311</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178838; 263678</t>
+          <t>219051; 273162</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>296365; 365898</t>
+          <t>297365; 371449</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>284649; 358179</t>
+          <t>281670; 355091</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>413012; 567137</t>
+          <t>526629; 597294</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>410937; 492949</t>
+          <t>412347; 497420</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>382863; 464351</t>
+          <t>383156; 466397</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>650438; 818617</t>
+          <t>762491; 855960</t>
         </is>
       </c>
     </row>
